--- a/docs/GroupConnect_Universite_2026-07-19.xlsx
+++ b/docs/GroupConnect_Universite_2026-07-19.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -449,6 +449,7 @@
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -474,7 +475,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Yazar(lar)</t>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Görünürlük</t>
         </is>
       </c>
     </row>
@@ -504,6 +510,11 @@
           <t>Ayşe Demir</t>
         </is>
       </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Yalnız yetkili</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -529,6 +540,11 @@
           <t>Ayşe Demir</t>
         </is>
       </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Yalnız yetkili</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -554,6 +570,11 @@
           <t>Mehmet Kaya</t>
         </is>
       </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Yalnız yetkili</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -581,6 +602,11 @@
           <t>Kaan Sezgin</t>
         </is>
       </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Yalnız yetkili</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -606,6 +632,11 @@
           <t>Kaan Sezgin</t>
         </is>
       </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Yalnız yetkili</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -629,6 +660,11 @@
       <c r="E7" s="3" t="inlineStr">
         <is>
           <t>Ece Yalman</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Yalnız yetkili</t>
         </is>
       </c>
     </row>
@@ -1255,16 +1291,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1300,7 +1338,17 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Yazar(lar)</t>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Görünürlük</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Üyeler Yazar mı</t>
         </is>
       </c>
     </row>
@@ -1340,6 +1388,16 @@
           <t>Ayşe Demir</t>
         </is>
       </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>Yalnız yetkili</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -1375,6 +1433,16 @@
           <t>Ayşe Demir</t>
         </is>
       </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Yalnız yetkili</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -1410,6 +1478,16 @@
           <t>Mehmet Kaya</t>
         </is>
       </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Yalnız yetkili</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -1442,7 +1520,17 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>Vedat Coşkun, Ayşe Demir</t>
+          <t>Vedat Coşkun</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Tüm üyeler</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>Evet</t>
         </is>
       </c>
     </row>
@@ -1477,7 +1565,17 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>— (özel grupta her üye yazar)</t>
+          <t>Vedat Coşkun</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Tüm üyeler</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>Evet</t>
         </is>
       </c>
     </row>
@@ -1512,7 +1610,17 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>— (özel grupta her üye yazar)</t>
+          <t>Elif Yılmaz</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Tüm üyeler</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>Evet</t>
         </is>
       </c>
     </row>
@@ -1547,7 +1655,17 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>— (özel grupta her üye yazar)</t>
+          <t>Mehmet Kaya</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Tüm üyeler</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>Evet</t>
         </is>
       </c>
     </row>
@@ -1587,6 +1705,16 @@
           <t>Kaan Sezgin</t>
         </is>
       </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Yalnız yetkili</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -1622,6 +1750,16 @@
           <t>Kaan Sezgin</t>
         </is>
       </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Yalnız yetkili</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -1655,6 +1793,16 @@
       <c r="G11" s="3" t="inlineStr">
         <is>
           <t>Ece Yalman</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Yalnız yetkili</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>Hayır</t>
         </is>
       </c>
     </row>
